--- a/tasks/finalpool/canvas-course-notion-wiki/groundtruth_workspace/course_catalog.xlsx
+++ b/tasks/finalpool/canvas-course-notion-wiki/groundtruth_workspace/course_catalog.xlsx
@@ -467,12 +467,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2015-06-26</t>
+          <t>2015-06-27</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -500,12 +500,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2015-06-19</t>
+          <t>2015-06-20</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -533,12 +533,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2015-06-26</t>
+          <t>2015-06-27</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -566,12 +566,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2015-06-19</t>
+          <t>2015-06-20</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2015-06-26</t>
+          <t>2015-06-27</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -632,12 +632,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2015-06-26</t>
+          <t>2015-06-27</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -665,12 +665,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2015-06-26</t>
+          <t>2015-06-27</t>
         </is>
       </c>
       <c r="E8" t="n">
